--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -2507,7 +2507,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 동물용 의약품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 판매·유통업</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 동물용 의약품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 판매·유통업</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -207,7 +207,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5개 대분류 · 24개 중분류 · 62개 소분류 — 정의는 소분류에만 둔다</t>
+          <t xml:space="preserve">5개 대분류 · 24개 중분류 · 61개 소분류 — 정의는 소분류에만 둔다</t>
         </is>
       </c>
     </row>
@@ -2576,74 +2576,74 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 활용한 동물용 의약품을 판매·유통하는 산업활동을 말한다. 동물약국의 동물용 의약품 소매를 포함한다. 사업자를 주된 상대로 하는 판매는 441로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 「그린바이오산업 육성에 관한 법률」 제2조제4호의 그린바이오제품을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 그린바이오 향장제품·생활제품의 유통과 동물약국의 그린바이오 동물용 의약품 소매를 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">47811</t>
+          <t xml:space="preserve">47811, 47859, 47999</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 「그린바이오산업 육성에 관한 법률」 제2조제4호의 그린바이오제품을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 그린바이오 향장제품·생활제품의 유통을 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">「그린바이오산업 육성에 관한 법률」 제13조에 따른 농업생명자원의 유전체 정보 등을 분석하여 디지털육종을 지원하는 유전체·표지·표현체 분석과 생물정보 컨설팅 서비스를 제공하는 산업활동을 말한다. 농림축산식품부가 지정하는 디지털육종 컨설팅·분석 전문기관의 서비스가 이에 해당한다. 품종 자체를 육성하는 연구개발은 111로, 분석 기술·플랫폼 자체의 연구개발은 162로 분류한다.</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">47859, 47999</t>
+          <t xml:space="preserve">72919, 63111</t>
         </is>
       </c>
     </row>
@@ -2670,22 +2670,22 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「그린바이오산업 육성에 관한 법률」 제13조에 따른 농업생명자원의 유전체 정보 등을 분석하여 디지털육종을 지원하는 유전체·표지·표현체 분석과 생물정보 컨설팅 서비스를 제공하는 산업활동을 말한다. 농림축산식품부가 지정하는 디지털육종 컨설팅·분석 전문기관의 서비스가 이에 해당한다. 품종 자체를 육성하는 연구개발은 111로, 분석 기술·플랫폼 자체의 연구개발은 162로 분류한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않는 그 밖의 그린바이오 관련 데이터를 수집·분석·가공하여 제공하는 산업활동을 말한다. 생물정보 데이터베이스·플랫폼 운영을 포함한다. 데이터 분석이 새로운 품종·소재·제품·기술의 개발로 이어지는 연구개발은 대분류 1의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">72919, 63111</t>
+          <t xml:space="preserve">63111, 63991, 62010, 58222</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2702,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 환경서비스업</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는 그 밖의 그린바이오 관련 데이터를 수집·분석·가공하여 제공하는 산업활동을 말한다. 생물정보 데이터베이스·플랫폼 운영을 포함한다. 데이터 분석이 새로운 품종·소재·제품·기술의 개발로 이어지는 연구개발은 대분류 1의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">곤충·미생물 등 그린바이오 생물자원을 이용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">63111, 63991, 62010, 58222</t>
+          <t xml:space="preserve">37022, 38210</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충·미생물 등 그린바이오 생물자원을 이용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
+          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 그린바이오 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 「농약관리법」 제2조제8호의 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">37022, 38210</t>
+          <t xml:space="preserve">74220, 01411</t>
         </is>
       </c>
     </row>
@@ -2786,72 +2786,30 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 그린바이오 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 「농약관리법」 제2조제8호의 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
+          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오 관련 서비스를 제공하는 산업활동을 말한다. 종자·미생물·곤충·천연물·식품·동물용 의약품 등 그린바이오 재화의 품질·성분·기능성·안전성·유효성을 정형화된 방법으로 시험·검정·분석하는 서비스(종자 검정, 미생물 동정, 유전자·성분 분석과 동물용 의약품의 비임상 시험 수탁), 그린바이오 재화 또는 그 생산·제조 공정이 법령·규격·표준에 적합한지를 검사·심사하여 인증하는 서비스, 종자·균주 등 생물자원의 정체성 유지에 특화된 보관·수송 서비스를 포함한다. 새로운 품종·소재·제품·기술의 개발을 목적으로 하는 수탁 연구는 대분류 1의 해당 소분류로, 디지털육종을 지원하는 유전체·생물정보 분석 서비스는 521로 분류한다. 단순 운송·보관은 제외하고, 그린바이오 기술에 관한 교육·훈련은 생명공학 기술을 적용하는 활동이 아니라 지식을 전달하는 활동이므로 제외한다(법 제10조의 전문인력 양성 지원체계에 속한다).</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74220, 01411</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오 관련 서비스를 제공하는 산업활동을 말한다. 종자·미생물·곤충·천연물·식품·동물용 의약품 등 그린바이오 재화의 품질·성분·기능성·안전성·유효성을 정형화된 방법으로 시험·검정·분석하는 서비스(종자 검정, 미생물 동정, 유전자·성분 분석과 동물용 의약품의 비임상 시험 수탁), 그린바이오 재화 또는 그 생산·제조 공정이 법령·규격·표준에 적합한지를 검사·심사하여 인증하는 서비스, 종자·균주 등 생물자원의 정체성 유지에 특화된 보관·수송 서비스를 포함한다. 새로운 품종·소재·제품·기술의 개발을 목적으로 하는 수탁 연구는 대분류 1의 해당 소분류로, 디지털육종을 지원하는 유전체·생물정보 분석 서비스는 521로 분류한다. 단순 운송·보관은 제외하고, 그린바이오 기술에 관한 교육·훈련은 생명공학 기술을 적용하는 활동이 아니라 지식을 전달하는 활동이므로 제외한다(법 제10조의 전문인력 양성 지원체계에 속한다).</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">52102, 72911, 72919, 52109, 52101</t>
         </is>
@@ -2893,16 +2851,16 @@
     <mergeCell ref="D50:D53"/>
     <mergeCell ref="C54:C57"/>
     <mergeCell ref="D54:D57"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="A49:A61"/>
-    <mergeCell ref="B49:B61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="A49:A60"/>
+    <mergeCell ref="B49:B60"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="A61:A65"/>
+    <mergeCell ref="B61:B65"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7249,12 +7207,12 @@
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -286,7 +286,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 새로운 종자·품종을 육성하거나 「종자산업법」 제2조제1호에 따른 씨앗·버섯 종균·묘목·포자·영양체의 형질·기능·증식공정·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다. 유전자변형식물체의 품종·형질·안전성 연구개발과 분자표지·유전체 분석을 이용한 육종을 포함한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 새로운 종자·품종을 육성하거나 증식용 또는 재배용으로 쓰이는 씨앗·버섯 종균·묘목·포자·영양체의 형질·기능·증식공정·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다. 유전자변형식물체의 품종·형질·안전성 연구개발과 분자표지·유전체 분석을 이용한 육종을 포함한다.</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「농업생명자원의 보존ㆍ관리 및 이용에 관한 법률」 제2조제1호에 따른 농업생명자원으로서의 미생물 등 재배·사육·발효에 투입하기 위한 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 「종자산업법」 제2조제1호에 따라 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물 등 재배·사육·발효에 투입하기 위한 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「곤충산업의 육성 및 지원에 관한 법률」 제2조제1호에 따른 곤충으로서 사육·증식에 투입하기 위한 것 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
+          <t xml:space="preserve">곤충으로서 사육·증식에 투입하기 위한 것 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 그 유래 물질 등 그린바이오를 활용하여 「농약관리법」 제2조제1호에 따른 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 또는 그 유래 물질 등 그린바이오를 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 또는 그 대사산물 등 그린바이오를 활용하여 「비료관리법」 제2조제1호에 따른 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량 목적의 미생물 제제 연구개발을 포함한다(같은 호의 토양개량용 자재, 같은 조 제3호의 부산물비료).</t>
+          <t xml:space="preserve">미생물 또는 그 대사산물 등 그린바이오를 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량용 자재·부산물비료 등 토양개량 목적의 미생물 제제 연구개발을 포함한다.</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 발효·효소 등 그린바이오를 활용하여 「사료관리법」 제2조제1호에 따른 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 14로 분류한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 또는 발효·효소 등 그린바이오를 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 14로 분류한다.</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">천연물·미생물·곤충 등 그린바이오 생물자원에서 유래한 물질을 식품 제조에 사용되는 원재료 또는 중간생산물로 개발하고, 그 성분·기능·추출·분리·정제·표준화·대량생산 또는 이용기술을 연구·개발하는 산업활동을 말한다. 기능성 소재와 그 밖의 식품소재를 모두 포함한다(법 제2조제2호마목). 대체식품의 소재를 목적으로 하는 연구개발은 134로, 발효공정·미생물 이용기술 자체의 연구개발은 133으로, 향장·생활제품용 소재를 목적으로 하는 연구개발은 15로 분류한다.</t>
+          <t xml:space="preserve">천연물·미생물·곤충 등 그린바이오 생물자원에서 유래한 물질을 식품 제조에 사용되는 원재료 또는 중간생산물로 개발하고, 그 성분·기능·추출·분리·정제·표준화·대량생산 또는 이용기술을 연구·개발하는 산업활동을 말한다. 기능성 소재와 그 밖의 식품소재를 모두 포함한다. 대체식품의 소재를 목적으로 하는 연구개발은 134로, 발효공정·미생물 이용기술 자체의 연구개발은 133으로, 향장·생활제품용 소재를 목적으로 하는 연구개발은 15로 분류한다.</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 「건강기능식품에 관한 법률」 제3조제1호에 따른 건강기능식품의 배합·제형·기능성·안전성 또는 제품기술을 연구·개발하는 산업활동을 말한다. 원재료·중간생산물 단계의 연구개발은 131로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 인체에 유용한 기능성을 가진 원료·성분으로 제조한 건강기능식품의 배합·제형·기능성·안전성 또는 제품기술을 연구·개발하는 산업활동을 말한다. 원재료·중간생산물 단계의 연구개발은 131로 분류한다.</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 「약사법」 제85조 및 「동물용의약품 등 취급규칙」 제2조제1항제1호의 동물용의약품 가운데 동물의 감염병을 예방하기 위한 항원·면역원·백신주·벡터·보조제·제제·생산공정·효능·안전성 또는 투여기술을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 동물용으로만 사용할 것을 목적으로 하는 의약품 가운데 동물의 감염병을 예방하기 위한 항원·면역원·백신주·벡터·보조제·제제·생산공정·효능·안전성 또는 투여기술을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업으로 분류되지 않는 「약사법」 제85조에 따른 그 밖의 그린바이오 동물용 의약품의 후보물질·유효성분·진단제·치료제·제제·생산공정·효능·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업으로 분류되지 않는 그 밖의 그린바이오 동물용 의약품의 후보물질·유효성분·진단제·치료제·제제·생산공정·효능·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 「화장품법」 제2조제1호의 화장품(같은 조 제2호의 기능성화장품과 제3호의2의 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품, 그리고 그 제조에 사용되는 소재·제형·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품, 그리고 그 제조에 사용되는 소재·제형·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오가 적용된 「종자산업법」 제2조제1호의 종자(증식용 또는 재배용 씨앗·버섯 종균·묘목·포자·영양체 등)를 증식·채종·육묘하여 종자로 생산하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">그린바이오가 적용된 종자(증식용 또는 재배용으로 쓰이는 씨앗·버섯 종균·묘목·포자·영양체 등)를 증식·채종·육묘하여 종자로 생산하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「마약류 관리에 관한 법률」 제2조제4호의 대마초(칸나비스 사티바 엘)를 그린바이오 소재의 제조에 원료로 사용하기 위하여 재배·생산하는 산업활동을 말한다. 섬유·종자 채취 목적의 재배는 같은 조 제5호라목의 대마재배자 허가를, 칸나비디올 등 그 밖의 소재 목적의 재배는 「규제자유특구 및 지역특화발전특구에 관한 규제특례법」에 따른 실증특례 등 별도의 법적 근거를 전제로 한다. 그린바이오 소재 제조와 연결되지 않는 재배는 제외하고, 대마 유래 소재의 추출·가공은 311로 분류한다.</t>
+          <t xml:space="preserve">대마초(칸나비스 사티바 엘)를 그린바이오 소재의 제조에 원료로 사용하기 위하여 재배·생산하는 산업활동을 말한다. 섬유·종자 채취 목적의 재배는 대마재배자 허가를, 칸나비디올 등 그 밖의 소재 목적의 재배는 규제자유특구의 실증특례 등 별도의 법적 근거를 전제로 한다. 그린바이오 소재 제조와 연결되지 않는 재배는 제외하고, 대마 유래 소재의 추출·가공은 311로 분류한다.</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「실험동물에 관한 법률」 제2조제2호에 따른 실험동물을 생물학적 정체성과 증식능력을 유지하면서 사육·증식하여 생산하는 산업활동을 말한다. 동물용 의약품·농자재·식품 등 그린바이오 분야의 연구개발·시험에 공급하는 생산으로 한정하며, 인체용 의약품 개발 등 그린바이오 외 분야에만 공급하는 생산은 제외한다.</t>
+          <t xml:space="preserve">동물실험을 목적으로 사용 또는 사육되는 실험동물을 생물학적 정체성과 증식능력을 유지하면서 사육·증식하여 생산하는 산업활동을 말한다. 동물용 의약품·농자재·식품 등 그린바이오 분야의 연구개발·시험에 공급하는 생산으로 한정하며, 인체용 의약품 개발 등 그린바이오 외 분야에만 공급하는 생산은 제외한다.</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는 「농업생명자원의 보존ㆍ관리 및 이용에 관한 법률」 제2조제1호에 따른 농업생명자원으로서의 미생물·곤충 등 그 밖의 생물자원을 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 미생물·곤충 등 그 밖의 생물자원을 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 「그린바이오산업 육성에 관한 법률」 제2조제5호의 그린바이오소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정한다 — 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 312로 분류한다. 소재용 식물 자체의 재배는 22의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정한다 — 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 312로 분류한다. 소재용 식물 자체의 재배는 22의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 「그린바이오산업 육성에 관한 법률」 제2조제5호의 그린바이오소재로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 290으로 분류한다.</t>
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물(그린바이오소재)로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 290으로 분류한다.</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충(범위는 113의 정의에 따른다) 또는 그 유래 물질을 건조·분쇄·추출·분리·정제·가공하여 「그린바이오산업 육성에 관한 법률」 제2조제5호의 그린바이오소재를 제조하는 산업활동을 말한다. 살아 있는 곤충의 사육·증식은 290으로 분류한다.</t>
+          <t xml:space="preserve">곤충(범위는 113의 정의에 따른다) 또는 그 유래 물질을 건조·분쇄·추출·분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오소재를 제조하는 산업활동을 말한다. 살아 있는 곤충의 사육·증식은 290으로 분류한다.</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물·미생물·곤충 유래 소재로 달리 분류되지 않는 그 밖의 「그린바이오산업 육성에 관한 법률」 제2조제5호의 그린바이오소재를 제조하는 산업활동을 말한다. 둘 이상의 유래가 혼합된 소재를 포함한다. 식품첨가물의 제조는 331로 분류한다.</t>
+          <t xml:space="preserve">식물·미생물·곤충 유래 소재로 달리 분류되지 않는 그 밖의 그린바이오소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 제조하는 산업활동을 말한다. 둘 이상의 유래가 혼합된 소재를 포함한다. 식품첨가물의 제조는 331로 분류한다.</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 그 유래 물질 등 그린바이오를 활용하여 「농약관리법」 제2조제1호에 따른 농약을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 또는 그 유래 물질 등 그린바이오를 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 또는 그 대사산물 등 그린바이오를 활용하여 「비료관리법」 제2조제1호에 따른 비료를 제조하는 산업활동을 말한다. 같은 호는 토양개량용 자재를 비료에 포함한다.</t>
+          <t xml:space="preserve">미생물 또는 그 대사산물 등 그린바이오를 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료(토양개량용 자재를 포함한다)를 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 발효·효소 등 그린바이오를 활용하여 「사료관리법」 제2조제1호에 따른 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 또는 발효·효소 등 그린바이오를 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 「식품위생법」 제2조제2호에 따른 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 식품의 제조·가공 과정에서 기능을 위하여 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특정 미생물·균주 또는 발효공정 제어기술 등 그린바이오를 직접 활용하여 「식품위생법」 제2조제1호의 식품 가운데 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품은 제외한다.</t>
+          <t xml:space="preserve">특정 미생물·균주 또는 발효공정 제어기술 등 그린바이오를 직접 활용하여 식품 가운데 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품은 제외한다.</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 「건강기능식품에 관한 법률」 제3조제1호에 따른 건강기능식품을 제조하는 산업활동을 말한다. 일반 건강보조식품은 제외한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 인체에 유용한 기능성을 가진 원료·성분으로 제조한 건강기능식품을 제조하는 산업활동을 말한다. 일반 건강보조식품은 제외한다.</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오 생물자원·소재 또는 생물공정을 직접 활용하여 「식품위생법」 제2조제1호의 그 밖의 식품을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오 생물자원·소재 또는 생물공정을 직접 활용하여 그 밖의 식품을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 「약사법」 제85조 및 「그린바이오산업 육성에 관한 법률 시행령」 제2조에 따라 동물용으로만 사용할 것을 목적으로 하는 의약품과 그 제제를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 동물용으로만 사용할 것을 목적으로 하는 의약품과 그 제제를 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 법정 관련 분야의 생물자원·소재에 생명공학 관련 기술을 적용하여 「화장품법」 제2조제1호의 화장품(같은 조 제2호의 기능성화장품과 제3호의2의 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 392로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등 법정 관련 분야의 생물자원·소재에 생명공학 관련 기술을 적용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 392로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 직접 활용하여 제조한 그 밖의 「그린바이오산업 육성에 관한 법률」 제2조제4호의 그린바이오제품을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 직접 활용하여 제조한 그 밖의 그린바이오제품을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원과 「그린바이오산업 육성에 관한 법률」 제2조제5호의 그린바이오소재를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충, 추출물·발효물·기능성 원료 등의 유통을 포함한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 2 또는 3의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">그린바이오 생물자원과 그린바이오소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충, 추출물·발효물·기능성 원료 등의 유통을 포함한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 2 또는 3의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「농약관리법」 제2조제7호의 판매업으로서 그린바이오를 활용한 농약을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 화학농약만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">농약판매업을 등록한 사업체로서 그린바이오를 활용한 농약을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 화학농약만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「비료관리법」 제2조제6호다목의 비료판매업자로서 그린바이오를 활용한 비료를 판매하는 산업활동을 말한다. 생명공학 관련 기술의 적용이 확인되지 않는 일반 비료만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">비료판매업자로서 그린바이오를 활용한 비료를 판매하는 산업활동을 말한다. 생명공학 관련 기술의 적용이 확인되지 않는 일반 비료만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「사료관리법」 제2조제9호의 판매업자로서 그린바이오를 활용한 사료를 판매하는 산업활동을 말한다. 생명공학 관련 기술의 적용이 확인되지 않는 일반 사료만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">사료판매업자로서 그린바이오를 활용한 사료를 판매하는 산업활동을 말한다. 생명공학 관련 기술의 적용이 확인되지 않는 일반 사료만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「건강기능식품에 관한 법률」 제4조제1항제3호의 건강기능식품판매업으로서 그린바이오를 활용한 건강기능식품을 판매하는 산업활동을 말한다. 개인의 생활습관·건강상태 등에 따라 소분·조합하여 판매하는 활동은 432로, 제조를 위탁하여 자기 상표로 유통하는 활동은 433으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">건강기능식품판매업으로서 그린바이오를 활용한 건강기능식품을 판매하는 산업활동을 말한다. 개인의 생활습관·건강상태 등에 따라 소분·조합하여 판매하는 활동은 432로, 제조를 위탁하여 자기 상표로 유통하는 활동은 433으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「건강기능식품에 관한 법률」 제4조제1항제4호의 맞춤형건강기능식품판매업으로서 그린바이오를 활용한 건강기능식품을 개인의 생활습관·건강상태 등에 따라 소분·조합하여 판매하는 산업활동을 말한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">맞춤형건강기능식품판매업으로서 그린바이오를 활용한 건강기능식품을 개인의 생활습관·건강상태 등에 따라 소분·조합하여 판매하는 산업활동을 말한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용한 식품 또는 식품첨가물을 스스로 제조·가공하지 아니하고 제조업자에게 의뢰하여 제조·가공한 것을 자기 상표로 유통·판매하는 산업활동을 말한다. 「식품위생법 시행령」 제21조제5호나목3)의 유통전문판매업으로서 그린바이오 식품을 취급하는 활동이 이에 해당한다. 원재료를 자기계정으로 제공하여 위탁 생산하는 경우는 대분류 3의 해당 제조업으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">그린바이오를 활용한 식품 또는 식품첨가물을 스스로 제조·가공하지 아니하고 제조업자에게 의뢰하여 제조·가공한 것을 자기 상표로 유통·판매하는 산업활동을 말한다. 식품 유통전문판매업으로서 그린바이오 식품을 취급하는 활동이 이에 해당한다. 원재료를 자기계정으로 제공하여 위탁 생산하는 경우는 대분류 3의 해당 제조업으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 활용한 식품과 식품소재를 판매·유통하는 산업활동을 말한다. 식품소재·식품첨가물의 도매와 「식품위생법 시행령」 제21조제5호나목의 식품판매업으로서 그린바이오 식품을 취급하는 활동을 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 활용한 식품과 식품소재를 판매·유통하는 산업활동을 말한다. 식품소재·식품첨가물의 도매와 식품판매업으로서 그린바이오 식품을 취급하는 활동을 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「약사법」 제45조에 따라 허가받은 동물용의약품 도매상으로서 그린바이오를 활용한 동물용 의약품을 구입하여 사업자에게 판매하거나 그 매매를 중개하는 산업활동을 말한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">허가받은 동물용 의약품 도매상으로서 그린바이오를 활용한 동물용 의약품을 구입하여 사업자에게 판매하거나 그 매매를 중개하는 산업활동을 말한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「동물용의약품 등 취급규칙」 제4조의2의 위탁제조판매업으로서 제조를 위탁하여 만든 그린바이오 동물용 의약품을 자기 상표로 유통·판매하는 산업활동을 말한다. 원재료를 자기계정으로 제공하여 위탁 생산하는 경우는 340으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">동물용 의약품 위탁제조판매업으로서 제조를 위탁하여 만든 그린바이오 동물용 의약품을 자기 상표로 유통·판매하는 산업활동을 말한다. 원재료를 자기계정으로 제공하여 위탁 생산하는 경우는 340으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 「그린바이오산업 육성에 관한 법률」 제2조제4호의 그린바이오제품을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 그린바이오 향장제품·생활제품의 유통과 동물약국의 그린바이오 동물용 의약품 소매를 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오를 활용하여 생산된 그린바이오제품을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 그린바이오 향장제품·생활제품의 유통과 동물약국의 그린바이오 동물용 의약품 소매를 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「그린바이오산업 육성에 관한 법률」 제13조에 따른 농업생명자원의 유전체 정보 등을 분석하여 디지털육종을 지원하는 유전체·표지·표현체 분석과 생물정보 컨설팅 서비스를 제공하는 산업활동을 말한다. 농림축산식품부가 지정하는 디지털육종 컨설팅·분석 전문기관의 서비스가 이에 해당한다. 품종 자체를 육성하는 연구개발은 111로, 분석 기술·플랫폼 자체의 연구개발은 162로 분류한다.</t>
+          <t xml:space="preserve">농업생명자원의 유전체 정보 등을 분석하여 디지털육종을 지원하는 유전체·표지·표현체 분석과 생물정보 컨설팅 서비스를 제공하는 산업활동을 말한다. 농림축산식품부가 지정하는 디지털육종 컨설팅·분석 전문기관의 서비스가 이에 해당한다. 품종 자체를 육성하는 연구개발은 111로, 분석 기술·플랫폼 자체의 연구개발은 162로 분류한다.</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 그린바이오 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 「농약관리법」 제2조제8호의 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
+          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 그린바이오 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오 관련 서비스를 제공하는 산업활동을 말한다. 종자·미생물·곤충·천연물·식품·동물용 의약품 등 그린바이오 재화의 품질·성분·기능성·안전성·유효성을 정형화된 방법으로 시험·검정·분석하는 서비스(종자 검정, 미생물 동정, 유전자·성분 분석과 동물용 의약품의 비임상 시험 수탁), 그린바이오 재화 또는 그 생산·제조 공정이 법령·규격·표준에 적합한지를 검사·심사하여 인증하는 서비스, 종자·균주 등 생물자원의 정체성 유지에 특화된 보관·수송 서비스를 포함한다. 새로운 품종·소재·제품·기술의 개발을 목적으로 하는 수탁 연구는 대분류 1의 해당 소분류로, 디지털육종을 지원하는 유전체·생물정보 분석 서비스는 521로 분류한다. 단순 운송·보관은 제외하고, 그린바이오 기술에 관한 교육·훈련은 생명공학 기술을 적용하는 활동이 아니라 지식을 전달하는 활동이므로 제외한다(법 제10조의 전문인력 양성 지원체계에 속한다).</t>
+          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오 관련 서비스를 제공하는 산업활동을 말한다. 종자·미생물·곤충·천연물·식품·동물용 의약품 등 그린바이오 재화의 품질·성분·기능성·안전성·유효성을 정형화된 방법으로 시험·검정·분석하는 서비스(종자 검정, 미생물 동정, 유전자·성분 분석과 동물용 의약품의 비임상 시험 수탁), 그린바이오 재화 또는 그 생산·제조 공정이 법령·규격·표준에 적합한지를 검사·심사하여 인증하는 서비스, 종자·균주 등 생물자원의 정체성 유지에 특화된 보관·수송 서비스를 포함한다. 새로운 품종·소재·제품·기술의 개발을 목적으로 하는 수탁 연구는 대분류 1의 해당 소분류로, 디지털육종을 지원하는 유전체·생물정보 분석 서비스는 521로 분류한다. 단순 운송·보관은 제외하고, 그린바이오 기술에 관한 교육·훈련은 생명공학 기술을 적용하는 활동이 아니라 지식을 전달하는 활동이므로 제외한다(산업활동이 아닌 인력양성 지원체계에 속한다).</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -328,7 +328,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물 등 재배·사육·발효에 투입하기 위한 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
+          <t xml:space="preserve">재배·사육·발효에 투입하기 위하여 농업에 실제적이거나 잠재적인 가치가 있는 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -328,7 +328,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">재배·사육·발효에 투입하기 위하여 농업에 실제적이거나 잠재적인 가치가 있는 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
+          <t xml:space="preserve">재배·사육이나 식품·농자재 생산을 위한 발효에 투입하기 위하여 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -370,7 +370,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충으로서 사육·증식에 투입하기 위한 것 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
+          <t xml:space="preserve">사육·증식에 투입하기 위하여 살아 있는 곤충 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -328,7 +328,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">재배·사육이나 식품·농자재 생산을 위한 발효에 투입하기 위하여 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 재배·사육이나 식품·농자재 생산을 위한 발효에 투입하는 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 111로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(12부터 16까지)로 분류한다.</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사육·증식에 투입하기 위하여 살아 있는 곤충 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 사육·증식에 투입하는 살아 있는 곤충 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존 축산물·수산물 등의 식감·풍미·영양 또는 기능을 대체하는 식품과 그 소재·배합·조직화공정·안전성 또는 제품기술을 연구·개발하는 산업활동을 말한다. 식물성·해조류 유래 대체육, 동물세포 배양육, 곤충 대체단백 및 미생물 발효 대체단백의 연구개발을 원료와 방식을 가리지 않고 포함한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 기존 축산물·수산물 등의 식감·풍미·영양 또는 기능을 대체하는 식품과 그 소재·배합·조직화공정·안전성 또는 제품기술을 연구·개발하는 산업활동을 말한다. 식물성·해조류 유래 대체육, 동물세포 배양육, 곤충 대체단백 및 미생물 발효 대체단백의 연구개발을 원료와 방식을 가리지 않고 포함한다.</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 미생물·곤충 등 그 밖의 생물자원을 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 미생물·곤충 등 그 밖의 생물자원을 그린바이오를 활용하여 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 그 유래 물질 등 그린바이오를 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 그 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 또는 그 대사산물 등 그린바이오를 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량용 자재·부산물비료 등 토양개량 목적의 미생물 제제 연구개발을 포함한다.</t>
+          <t xml:space="preserve">미생물 등 그린바이오 생물자원이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량용 자재·부산물비료 등 토양개량 목적의 미생물 제제 연구개발을 포함한다.</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 발효·효소 등 그린바이오를 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 14로 분류한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 14로 분류한다.</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 그 유래 물질 등 그린바이오를 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 그 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 또는 그 대사산물 등 그린바이오를 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료(토양개량용 자재를 포함한다)를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물 등 그린바이오 생물자원이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료(토양개량용 자재를 포함한다)를 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 또는 발효·효소 등 그린바이오를 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 식품의 제조·가공 과정에서 기능을 위하여 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 식품의 제조·가공 과정에서 기능을 위하여 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등을 비롯하여 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특정 미생물·균주 또는 발효공정 제어기술 등 그린바이오를 직접 활용하여 식품 가운데 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품은 제외한다.</t>
+          <t xml:space="preserve">특정 미생물·균주 또는 발효공정 제어기술을 직접 활용하여 식품 가운데 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품은 제외한다.</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -412,7 +412,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는 그 밖의 그린바이오 생물자원과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 그 밖의 살아 있는 생물자원과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 그 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물이나 천연물 등 생물 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 그린바이오 생물자원이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량용 자재·부산물비료 등 토양개량 목적의 미생물 제제 연구개발을 포함한다.</t>
+          <t xml:space="preserve">살아 있는 미생물이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량용 자재·부산물비료 등 토양개량 목적의 미생물 제제 연구개발을 포함한다.</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 14로 분류한다.</t>
+          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물, 천연물 등 생물 유래 물질 또는 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 14로 분류한다.</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약·바이오비료·바이오사료로 분류되지 않는 그 밖의 그린바이오 농자재와 그 소재·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 그린바이오 생물자원 또는 미생물 발효로 생산한 생분해성 소재를 이용한 농업용 필름·육묘용기, 미생물·천연물을 이용한 축사 환경개선제, 비료·농약에 해당하지 않는 작물 생육 촉진 자재 등의 연구개발을 포함한다. 종자는 111로, 동물용 의약품은 14로 분류한다. 농기계·시설·장비의 연구개발과 그린바이오가 기여하지 않는 석유 유래 자재의 연구개발은 제외한다.</t>
+          <t xml:space="preserve">바이오농약·바이오비료·바이오사료로 분류되지 않는 그 밖의 그린바이오 농자재와 그 소재·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 생물자원 또는 미생물 발효로 생산한 생분해성 소재를 이용한 농업용 필름·육묘용기, 미생물·천연물을 이용한 축사 환경개선제, 비료·농약에 해당하지 않는 작물 생육 촉진 자재 등의 연구개발을 포함한다. 종자는 111로, 동물용 의약품은 14로 분류한다. 농기계·시설·장비의 연구개발과 그린바이오가 기여하지 않는 석유 유래 자재의 연구개발은 제외한다.</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">천연물·미생물·곤충 등 그린바이오 생물자원에서 유래한 물질을 식품 제조에 사용되는 원재료 또는 중간생산물로 개발하고, 그 성분·기능·추출·분리·정제·표준화·대량생산 또는 이용기술을 연구·개발하는 산업활동을 말한다. 기능성 소재와 그 밖의 식품소재를 모두 포함한다. 대체식품의 소재를 목적으로 하는 연구개발은 134로, 발효공정·미생물 이용기술 자체의 연구개발은 133으로, 향장·생활제품용 소재를 목적으로 하는 연구개발은 15로 분류한다.</t>
+          <t xml:space="preserve">미생물·곤충·식물 등 살아 있는 생물에서 유래한 천연물 등의 물질을 식품 제조에 사용되는 원재료 또는 중간생산물로 개발하고, 그 성분·기능·추출·분리·정제·표준화·대량생산 또는 이용기술을 연구·개발하는 산업활동을 말한다. 기능성 소재와 그 밖의 식품소재를 모두 포함한다. 대체식품의 소재를 목적으로 하는 연구개발은 134로, 발효공정·미생물 이용기술 자체의 연구개발은 133으로, 향장·생활제품용 소재를 목적으로 하는 연구개발은 15로 분류한다.</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충·미생물 등 그린바이오 생물자원을 이용하여 유기성 폐자원의 처리, 병해충 방제, 축사·농지·농업용수 등 농업환경의 관리·개선에 사용되는 기술·공정 또는 제제를 연구·개발하는 산업활동을 말한다. 농약 제제를 목적으로 하는 연구개발은 121로, 비료·토양개량 제제는 122로, 생물자원 자체의 발굴·개량은 11의 해당 소분류로 분류한다. 환경서비스의 제공 자체는 53의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원을 이용하여 유기성 폐자원의 처리, 병해충 방제, 축사·농지·농업용수 등 농업환경의 관리·개선에 사용되는 기술·공정 또는 제제를 연구·개발하는 산업활동을 말한다. 농약 제제를 목적으로 하는 연구개발은 121로, 비료·토양개량 제제는 122로, 생물자원 자체의 발굴·개량은 11의 해당 소분류로 분류한다. 환경서비스의 제공 자체는 53의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 그 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물이나 천연물 등 생물 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 그린바이오 생물자원이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료(토양개량용 자재를 포함한다)를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">살아 있는 미생물이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료(토양개량용 자재를 포함한다)를 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 그린바이오 생물자원이나 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물, 천연물 등 생물 유래 물질 또는 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약·바이오비료·바이오사료로 달리 분류되지 않는 그 밖의 그린바이오 농자재를 제조하는 산업활동을 말한다. 그린바이오 생물자원 또는 미생물 발효로 생산한 생분해성 소재를 이용한 농업용 필름·육묘용기, 미생물·천연물을 이용한 축사 환경개선제, 비료·농약에 해당하지 않는 작물 생육 촉진 자재의 제조를 포함한다. 종자의 생산은 210으로, 동물용 의약품의 제조는 340으로 분류한다. 농기계·시설·장비와 그린바이오가 기여하지 않는 석유 유래 자재는 제외한다.</t>
+          <t xml:space="preserve">바이오농약·바이오비료·바이오사료로 달리 분류되지 않는 그 밖의 그린바이오 농자재를 제조하는 산업활동을 말한다. 생물자원 또는 미생물 발효로 생산한 생분해성 소재를 이용한 농업용 필름·육묘용기, 미생물·천연물을 이용한 축사 환경개선제, 비료·농약에 해당하지 않는 작물 생육 촉진 자재의 제조를 포함한다. 종자의 생산은 210으로, 동물용 의약품의 제조는 340으로 분류한다. 농기계·시설·장비와 그린바이오가 기여하지 않는 석유 유래 자재는 제외한다.</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물·미생물·곤충·세포배양 산물 등 그린바이오 생물자원·소재 또는 생물공정을 활용하여 기존 축산물·수산물 등의 식감·풍미·영양 또는 기능을 대체하는 식품을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">식물·미생물·곤충과 그 세포배양 산물 등 생물자원·소재 또는 생물공정을 활용하여 기존 축산물·수산물 등의 식감·풍미·영양 또는 기능을 대체하는 식품을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오 생물자원·소재 또는 생물공정을 직접 활용하여 그 밖의 식품을 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 생물자원·소재 또는 생물공정을 직접 활용하여 그 밖의 식품을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원과 그린바이오소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충, 추출물·발효물·기능성 원료 등의 유통을 포함한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 2 또는 3의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충 등 살아 있는 생물자원과 추출물·발효물·기능성 원료 등 그린바이오소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 2 또는 3의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충·미생물 등 그린바이오 생물자원을 이용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
+          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원을 이용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 그린바이오 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
+          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -412,7 +412,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 그 밖의 살아 있는 생물자원과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 그 밖의 살아 있는 생물자원(농업생물자원)과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 미생물·곤충 등 그 밖의 생물자원을 그린바이오를 활용하여 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 미생물·곤충 등 그 밖의 생물자원(농업생물자원)을 그린바이오를 활용하여 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물(그린바이오소재)로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 290으로 분류한다.</t>
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물(농업생물자원)을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물(그린바이오소재)로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 290으로 분류한다.</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -412,7 +412,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 그 밖의 살아 있는 생물자원(농업생물자원)과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 활용하여, 농업에 실제적이거나 잠재적인 가치가 있는 그 밖의 살아 있는 생물자원(농업생물자원)과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정한다 — 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 312로 분류한다. 소재용 식물 자체의 재배는 22의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정하며, 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 312로 분류한다. 소재용 식물 자체의 재배는 22의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 식품의 제조·가공 과정에서 기능을 위하여 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등을 비롯하여 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여, 식품을 제조·가공·조리하거나 보존하는 과정에서 감미·착색·표백·산화방지 등의 목적으로 식품에 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등을 비롯하여 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여, 식품을 제조·가공·조리하거나 보존하는 과정에서 감미·착색·표백·산화방지 등의 목적으로 식품에 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 미생물 발효로 생산한 효소·감미료·보존료 등을 비롯하여 유래를 가리지 않고 식품첨가물의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여, 식품을 제조·가공·조리하거나 보존하는 과정에서 감미·착색·표백·산화방지 등의 목적으로 식품에 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 식품첨가물이 유래한 생물자원의 종류는 가리지 않으며, 미생물 발효로 생산한 효소·감미료·보존료 등의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 31의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특정 미생물·균주 또는 발효공정 제어기술을 직접 활용하여 식품 가운데 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품은 제외한다.</t>
+          <t xml:space="preserve">선별하거나 개량한 특정 미생물·균주를 접종하거나 발효공정 제어기술을 직접 활용하여 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품의 제조는 제외한다.</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 생활에 사용하는 물품과 그 제조에 사용되는 소재·제형 또는 효능을 연구·개발하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오 소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 연구개발을 포함한다. 인체에 직접 사용하는 향장제품은 151로, 소재 자체의 연구개발은 131 또는 190으로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 생활에 사용하는 물품과 그 제조에 사용되는 소재·제형 또는 효능을 연구·개발하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 연구개발을 포함한다. 인체에 직접 사용하는 향장제품은 151로, 소재 자체의 연구개발은 131 또는 190으로 분류한다.</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 법정 관련 분야의 생물자원·소재에 생명공학 관련 기술을 적용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 392로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오소재를 사용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 392로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등 법정 관련 분야의 생물자원·소재에 생명공학 관련 기술을 적용하여 생활에 사용하는 물품을 제조하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오 소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 제조를 포함한다. 인체에 직접 사용하는 향장제품은 391로, 원단·성형체 등 소재 단계의 제조는 31의 해당 소분류로 분류한다. 단순 천연원료 배합제품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오소재를 사용하여 생활에 사용하는 물품을 제조하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 제조를 포함한다. 인체에 직접 사용하는 향장제품은 391로, 원단·성형체 등 소재 단계의 제조는 31의 해당 소분류로 분류한다. 단순 천연원료 배합제품은 제외한다.</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 생활에 사용하는 물품과 그 제조에 사용되는 소재·제형 또는 효능을 연구·개발하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 연구개발을 포함한다. 인체에 직접 사용하는 향장제품은 151로, 소재 자체의 연구개발은 131 또는 190으로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 생활에 사용하는 물품과 그 제조에 사용되는 소재·제형 또는 효능을 연구·개발하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오 소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 연구개발을 포함한다. 인체에 직접 사용하는 향장제품은 151로, 소재 자체의 연구개발은 131 또는 190으로 분류한다.</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정하며, 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 312로 분류한다. 소재용 식물 자체의 재배는 22의 해당 소분류로 분류한다.</t>
+          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오 소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정하며, 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 312로 분류한다. 소재용 식물 자체의 재배는 22의 해당 소분류로 분류한다.</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물(농업생물자원)을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물(그린바이오소재)로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 290으로 분류한다.</t>
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물(농업생물자원)을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물(그린바이오 소재)로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 290으로 분류한다.</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충(범위는 113의 정의에 따른다) 또는 그 유래 물질을 건조·분쇄·추출·분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오소재를 제조하는 산업활동을 말한다. 살아 있는 곤충의 사육·증식은 290으로 분류한다.</t>
+          <t xml:space="preserve">곤충(범위는 113의 정의에 따른다) 또는 그 유래 물질을 건조·분쇄·추출·분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오 소재를 제조하는 산업활동을 말한다. 살아 있는 곤충의 사육·증식은 290으로 분류한다.</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식물·미생물·곤충 유래 소재로 달리 분류되지 않는 그 밖의 그린바이오소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 제조하는 산업활동을 말한다. 둘 이상의 유래가 혼합된 소재를 포함한다. 식품첨가물의 제조는 331로 분류한다.</t>
+          <t xml:space="preserve">식물·미생물·곤충 유래 소재로 달리 분류되지 않는 그 밖의 그린바이오 소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 제조하는 산업활동을 말한다. 둘 이상의 유래가 혼합된 소재를 포함한다. 식품첨가물의 제조는 331로 분류한다.</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오소재를 사용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 392로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오 소재를 사용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 392로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오소재를 사용하여 생활에 사용하는 물품을 제조하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 제조를 포함한다. 인체에 직접 사용하는 향장제품은 391로, 원단·성형체 등 소재 단계의 제조는 31의 해당 소분류로 분류한다. 단순 천연원료 배합제품은 제외한다.</t>
+          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오 소재를 사용하여 생활에 사용하는 물품을 제조하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오 소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 제조를 포함한다. 인체에 직접 사용하는 향장제품은 391로, 원단·성형체 등 소재 단계의 제조는 31의 해당 소분류로 분류한다. 단순 천연원료 배합제품은 제외한다.</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충 등 살아 있는 생물자원과 추출물·발효물·기능성 원료 등 그린바이오소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 2 또는 3의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
+          <t xml:space="preserve">종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충 등 살아 있는 생물자원과 추출물·발효물·기능성 원료 등 그린바이오 소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 2 또는 3의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 2 또는 3의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -370,7 +370,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 사육·증식에 투입하는 살아 있는 곤충 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 사육·증식에 투입하는 살아 있는 곤충 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 사육·증식의 바탕이 되는 우수 종충(種蟲)의 개발을 포함한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -286,7 +286,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오를 활용하여 새로운 종자·품종을 육성하거나 증식용 또는 재배용으로 쓰이는 씨앗·버섯 종균·묘목·포자·영양체의 형질·기능·증식공정·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다. 유전자변형식물체의 품종·형질·안전성 연구개발과 분자표지·유전체 분석을 이용한 육종을 포함한다.</t>
+          <t xml:space="preserve">그린바이오를 활용하여 새로운 종자·품종을 육성하거나 증식용 또는 재배용으로 쓰이는 씨앗·버섯 종균·묘목·포자·영양체의 형질·기능·증식공정·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다. 유전자변형식물체의 품종·형질·안전성 연구개발과 방사선육종·배수체육종·유전체육종·디지털육종 등의 육종을 포함한다.</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -2722,7 +2722,7 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원을 이용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
+          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원(농업생물자원)에 생명공학 관련 기술을 적용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -2722,7 +2722,7 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원(농업생물자원)에 생명공학 관련 기술을 적용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
+          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원에 생명공학 관련 기술을 적용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 323으로, 분변토 비료의 제조는 322로 분류한다.</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_5차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_5차.xlsx
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 생물자원을 핵심 수단으로 삼아 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
+          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 생물자원을 핵심 수단으로 삼아, 생명공학 관련 기술과 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
